--- a/public/plantilla-matriz-aspectos.xlsx
+++ b/public/plantilla-matriz-aspectos.xlsx
@@ -549,7 +549,7 @@
     <xf numFmtId="14" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-matriz-aspectos.xlsx
+++ b/public/plantilla-matriz-aspectos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="1" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz Aspectos e Impactos" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-matriz-aspectos.xlsx
+++ b/public/plantilla-matriz-aspectos.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Matriz Aspectos e Impactos" sheetId="1" state="visible" r:id="rId1"/>
@@ -15,7 +15,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+  <numFmts count="0"/>
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -138,6 +139,10 @@
       <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -510,7 +515,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -720,6 +725,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2353,6 +2404,74 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2701,7 +2820,7 @@
     <tabColor theme="4" tint="0.3999755851924192"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Q33"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col width="5" customWidth="1" style="33" min="1" max="1"/>
@@ -2883,11 +3002,11 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="31" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="22" t="n"/>
+      <c r="C11" s="84" t="n"/>
+      <c r="D11" s="85" t="n"/>
+      <c r="E11" s="85" t="n"/>
+      <c r="F11" s="85" t="n"/>
+      <c r="G11" s="86" t="n"/>
       <c r="H11" s="25" t="inlineStr">
         <is>
           <t>Ubicación</t>
@@ -2895,12 +3014,12 @@
       </c>
       <c r="I11" s="30" t="n"/>
       <c r="J11" s="22" t="n"/>
-      <c r="K11" s="31" t="n"/>
-      <c r="L11" s="30" t="n"/>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="30" t="n"/>
-      <c r="O11" s="30" t="n"/>
-      <c r="P11" s="22" t="n"/>
+      <c r="K11" s="84" t="n"/>
+      <c r="L11" s="85" t="n"/>
+      <c r="M11" s="85" t="n"/>
+      <c r="N11" s="85" t="n"/>
+      <c r="O11" s="85" t="n"/>
+      <c r="P11" s="86" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="33">
       <c r="A12" s="25" t="inlineStr">
@@ -2909,11 +3028,11 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="31" t="n"/>
-      <c r="D12" s="30" t="n"/>
-      <c r="E12" s="30" t="n"/>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="84" t="n"/>
+      <c r="D12" s="85" t="n"/>
+      <c r="E12" s="85" t="n"/>
+      <c r="F12" s="85" t="n"/>
+      <c r="G12" s="86" t="n"/>
       <c r="H12" s="25" t="inlineStr">
         <is>
           <t>Elaboró</t>
@@ -2921,12 +3040,12 @@
       </c>
       <c r="I12" s="30" t="n"/>
       <c r="J12" s="22" t="n"/>
-      <c r="K12" s="31" t="n"/>
-      <c r="L12" s="30" t="n"/>
-      <c r="M12" s="30" t="n"/>
-      <c r="N12" s="30" t="n"/>
-      <c r="O12" s="30" t="n"/>
-      <c r="P12" s="22" t="n"/>
+      <c r="K12" s="84" t="n"/>
+      <c r="L12" s="85" t="n"/>
+      <c r="M12" s="85" t="n"/>
+      <c r="N12" s="85" t="n"/>
+      <c r="O12" s="85" t="n"/>
+      <c r="P12" s="86" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="33">
       <c r="A13" s="25" t="inlineStr">
@@ -2935,24 +3054,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="36" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="87" t="n"/>
+      <c r="D13" s="86" t="n"/>
       <c r="E13" s="25" t="inlineStr">
         <is>
           <t>Última actualización</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="36" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="87" t="n"/>
+      <c r="H13" s="86" t="n"/>
       <c r="I13" s="25" t="inlineStr">
         <is>
           <t>Versión</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="44" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="88" t="n"/>
+      <c r="L13" s="86" t="n"/>
       <c r="M13" s="75" t="n"/>
       <c r="N13" s="38" t="n"/>
       <c r="O13" s="38" t="n"/>
@@ -3059,294 +3178,294 @@
       <c r="P15" s="28" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1" s="33">
-      <c r="A16" s="48" t="n">
+      <c r="A16" s="89" t="n">
         <v>1</v>
       </c>
-      <c r="B16" s="46" t="n"/>
-      <c r="C16" s="46" t="n"/>
-      <c r="D16" s="46" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="48" t="n"/>
-      <c r="G16" s="48" t="n"/>
-      <c r="H16" s="48" t="n"/>
-      <c r="I16" s="48" t="n"/>
-      <c r="J16" s="48">
+      <c r="B16" s="90" t="n"/>
+      <c r="C16" s="90" t="n"/>
+      <c r="D16" s="90" t="n"/>
+      <c r="E16" s="91" t="n"/>
+      <c r="F16" s="92" t="n"/>
+      <c r="G16" s="92" t="n"/>
+      <c r="H16" s="92" t="n"/>
+      <c r="I16" s="92" t="n"/>
+      <c r="J16" s="89">
         <f>IF(OR(H16="",I16=""),"",VALUE(H16)*VALUE(I16))</f>
         <v/>
       </c>
-      <c r="K16" s="48">
+      <c r="K16" s="89">
         <f>IF(J16="","",IF(J16&gt;=15,"Alto",IF(J16&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L16" s="48">
+      <c r="L16" s="89">
         <f>IF(J16="","",IF(G16="Positivo","Positivo",IF(OR(K16="Alto",F16="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M16" s="46" t="n"/>
-      <c r="N16" s="46" t="n"/>
-      <c r="O16" s="81" t="n"/>
-      <c r="P16" s="82" t="n"/>
+      <c r="M16" s="90" t="n"/>
+      <c r="N16" s="90" t="n"/>
+      <c r="O16" s="93" t="n"/>
+      <c r="P16" s="94" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="33">
-      <c r="A17" s="48" t="n">
+      <c r="A17" s="89" t="n">
         <v>2</v>
       </c>
-      <c r="B17" s="46" t="n"/>
-      <c r="C17" s="46" t="n"/>
-      <c r="D17" s="46" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="48" t="n"/>
-      <c r="G17" s="48" t="n"/>
-      <c r="H17" s="48" t="n"/>
-      <c r="I17" s="48" t="n"/>
-      <c r="J17" s="48">
+      <c r="B17" s="90" t="n"/>
+      <c r="C17" s="90" t="n"/>
+      <c r="D17" s="90" t="n"/>
+      <c r="E17" s="91" t="n"/>
+      <c r="F17" s="92" t="n"/>
+      <c r="G17" s="92" t="n"/>
+      <c r="H17" s="92" t="n"/>
+      <c r="I17" s="92" t="n"/>
+      <c r="J17" s="89">
         <f>IF(OR(H17="",I17=""),"",VALUE(H17)*VALUE(I17))</f>
         <v/>
       </c>
-      <c r="K17" s="48">
+      <c r="K17" s="89">
         <f>IF(J17="","",IF(J17&gt;=15,"Alto",IF(J17&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L17" s="48">
+      <c r="L17" s="89">
         <f>IF(J17="","",IF(G17="Positivo","Positivo",IF(OR(K17="Alto",F17="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M17" s="46" t="n"/>
-      <c r="N17" s="46" t="n"/>
-      <c r="O17" s="83" t="n"/>
-      <c r="P17" s="22" t="n"/>
+      <c r="M17" s="90" t="n"/>
+      <c r="N17" s="90" t="n"/>
+      <c r="O17" s="84" t="n"/>
+      <c r="P17" s="86" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1" s="33">
-      <c r="A18" s="48" t="n">
+      <c r="A18" s="89" t="n">
         <v>3</v>
       </c>
-      <c r="B18" s="46" t="n"/>
-      <c r="C18" s="46" t="n"/>
-      <c r="D18" s="46" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="48" t="n"/>
-      <c r="G18" s="48" t="n"/>
-      <c r="H18" s="48" t="n"/>
-      <c r="I18" s="48" t="n"/>
-      <c r="J18" s="48">
+      <c r="B18" s="90" t="n"/>
+      <c r="C18" s="90" t="n"/>
+      <c r="D18" s="90" t="n"/>
+      <c r="E18" s="91" t="n"/>
+      <c r="F18" s="92" t="n"/>
+      <c r="G18" s="92" t="n"/>
+      <c r="H18" s="92" t="n"/>
+      <c r="I18" s="92" t="n"/>
+      <c r="J18" s="89">
         <f>IF(OR(H18="",I18=""),"",VALUE(H18)*VALUE(I18))</f>
         <v/>
       </c>
-      <c r="K18" s="48">
+      <c r="K18" s="89">
         <f>IF(J18="","",IF(J18&gt;=15,"Alto",IF(J18&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L18" s="48">
+      <c r="L18" s="89">
         <f>IF(J18="","",IF(G18="Positivo","Positivo",IF(OR(K18="Alto",F18="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M18" s="46" t="n"/>
-      <c r="N18" s="46" t="n"/>
-      <c r="O18" s="83" t="n"/>
-      <c r="P18" s="22" t="n"/>
+      <c r="M18" s="90" t="n"/>
+      <c r="N18" s="90" t="n"/>
+      <c r="O18" s="84" t="n"/>
+      <c r="P18" s="86" t="n"/>
     </row>
     <row r="19" ht="36" customHeight="1" s="33">
-      <c r="A19" s="48" t="n">
+      <c r="A19" s="89" t="n">
         <v>4</v>
       </c>
-      <c r="B19" s="46" t="n"/>
-      <c r="C19" s="46" t="n"/>
-      <c r="D19" s="46" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="48" t="n"/>
-      <c r="G19" s="48" t="n"/>
-      <c r="H19" s="48" t="n"/>
-      <c r="I19" s="48" t="n"/>
-      <c r="J19" s="48">
+      <c r="B19" s="90" t="n"/>
+      <c r="C19" s="90" t="n"/>
+      <c r="D19" s="90" t="n"/>
+      <c r="E19" s="91" t="n"/>
+      <c r="F19" s="92" t="n"/>
+      <c r="G19" s="92" t="n"/>
+      <c r="H19" s="92" t="n"/>
+      <c r="I19" s="92" t="n"/>
+      <c r="J19" s="89">
         <f>IF(OR(H19="",I19=""),"",VALUE(H19)*VALUE(I19))</f>
         <v/>
       </c>
-      <c r="K19" s="48">
+      <c r="K19" s="89">
         <f>IF(J19="","",IF(J19&gt;=15,"Alto",IF(J19&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L19" s="48">
+      <c r="L19" s="89">
         <f>IF(J19="","",IF(G19="Positivo","Positivo",IF(OR(K19="Alto",F19="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M19" s="46" t="n"/>
-      <c r="N19" s="46" t="n"/>
-      <c r="O19" s="83" t="n"/>
-      <c r="P19" s="22" t="n"/>
+      <c r="M19" s="90" t="n"/>
+      <c r="N19" s="90" t="n"/>
+      <c r="O19" s="84" t="n"/>
+      <c r="P19" s="86" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1" s="33">
-      <c r="A20" s="48" t="n">
+      <c r="A20" s="89" t="n">
         <v>5</v>
       </c>
-      <c r="B20" s="46" t="n"/>
-      <c r="C20" s="46" t="n"/>
-      <c r="D20" s="46" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="48" t="n"/>
-      <c r="G20" s="48" t="n"/>
-      <c r="H20" s="48" t="n"/>
-      <c r="I20" s="48" t="n"/>
-      <c r="J20" s="48">
+      <c r="B20" s="90" t="n"/>
+      <c r="C20" s="90" t="n"/>
+      <c r="D20" s="90" t="n"/>
+      <c r="E20" s="91" t="n"/>
+      <c r="F20" s="92" t="n"/>
+      <c r="G20" s="92" t="n"/>
+      <c r="H20" s="92" t="n"/>
+      <c r="I20" s="92" t="n"/>
+      <c r="J20" s="89">
         <f>IF(OR(H20="",I20=""),"",VALUE(H20)*VALUE(I20))</f>
         <v/>
       </c>
-      <c r="K20" s="48">
+      <c r="K20" s="89">
         <f>IF(J20="","",IF(J20&gt;=15,"Alto",IF(J20&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L20" s="48">
+      <c r="L20" s="89">
         <f>IF(J20="","",IF(G20="Positivo","Positivo",IF(OR(K20="Alto",F20="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M20" s="46" t="n"/>
-      <c r="N20" s="46" t="n"/>
-      <c r="O20" s="83" t="n"/>
-      <c r="P20" s="22" t="n"/>
+      <c r="M20" s="90" t="n"/>
+      <c r="N20" s="90" t="n"/>
+      <c r="O20" s="84" t="n"/>
+      <c r="P20" s="86" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1" s="33">
-      <c r="A21" s="48" t="n">
+      <c r="A21" s="89" t="n">
         <v>6</v>
       </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="48" t="n"/>
-      <c r="G21" s="48" t="n"/>
-      <c r="H21" s="48" t="n"/>
-      <c r="I21" s="48" t="n"/>
-      <c r="J21" s="48">
+      <c r="B21" s="90" t="n"/>
+      <c r="C21" s="90" t="n"/>
+      <c r="D21" s="90" t="n"/>
+      <c r="E21" s="91" t="n"/>
+      <c r="F21" s="92" t="n"/>
+      <c r="G21" s="92" t="n"/>
+      <c r="H21" s="92" t="n"/>
+      <c r="I21" s="92" t="n"/>
+      <c r="J21" s="89">
         <f>IF(OR(H21="",I21=""),"",VALUE(H21)*VALUE(I21))</f>
         <v/>
       </c>
-      <c r="K21" s="48">
+      <c r="K21" s="89">
         <f>IF(J21="","",IF(J21&gt;=15,"Alto",IF(J21&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L21" s="48">
+      <c r="L21" s="89">
         <f>IF(J21="","",IF(G21="Positivo","Positivo",IF(OR(K21="Alto",F21="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M21" s="46" t="n"/>
-      <c r="N21" s="46" t="n"/>
-      <c r="O21" s="83" t="n"/>
-      <c r="P21" s="22" t="n"/>
+      <c r="M21" s="90" t="n"/>
+      <c r="N21" s="90" t="n"/>
+      <c r="O21" s="84" t="n"/>
+      <c r="P21" s="86" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="33">
-      <c r="A22" s="48" t="n">
+      <c r="A22" s="89" t="n">
         <v>7</v>
       </c>
-      <c r="B22" s="46" t="n"/>
-      <c r="C22" s="46" t="n"/>
-      <c r="D22" s="46" t="n"/>
-      <c r="E22" s="14" t="n"/>
-      <c r="F22" s="48" t="n"/>
-      <c r="G22" s="48" t="n"/>
-      <c r="H22" s="48" t="n"/>
-      <c r="I22" s="48" t="n"/>
-      <c r="J22" s="48">
+      <c r="B22" s="90" t="n"/>
+      <c r="C22" s="90" t="n"/>
+      <c r="D22" s="90" t="n"/>
+      <c r="E22" s="91" t="n"/>
+      <c r="F22" s="92" t="n"/>
+      <c r="G22" s="92" t="n"/>
+      <c r="H22" s="92" t="n"/>
+      <c r="I22" s="92" t="n"/>
+      <c r="J22" s="89">
         <f>IF(OR(H22="",I22=""),"",VALUE(H22)*VALUE(I22))</f>
         <v/>
       </c>
-      <c r="K22" s="48">
+      <c r="K22" s="89">
         <f>IF(J22="","",IF(J22&gt;=15,"Alto",IF(J22&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L22" s="48">
+      <c r="L22" s="89">
         <f>IF(J22="","",IF(G22="Positivo","Positivo",IF(OR(K22="Alto",F22="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M22" s="46" t="n"/>
-      <c r="N22" s="46" t="n"/>
-      <c r="O22" s="83" t="n"/>
-      <c r="P22" s="22" t="n"/>
+      <c r="M22" s="90" t="n"/>
+      <c r="N22" s="90" t="n"/>
+      <c r="O22" s="84" t="n"/>
+      <c r="P22" s="86" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="33">
-      <c r="A23" s="48" t="n">
+      <c r="A23" s="89" t="n">
         <v>8</v>
       </c>
-      <c r="B23" s="46" t="n"/>
-      <c r="C23" s="46" t="n"/>
-      <c r="D23" s="46" t="n"/>
-      <c r="E23" s="14" t="n"/>
-      <c r="F23" s="48" t="n"/>
-      <c r="G23" s="48" t="n"/>
-      <c r="H23" s="48" t="n"/>
-      <c r="I23" s="48" t="n"/>
-      <c r="J23" s="48">
+      <c r="B23" s="90" t="n"/>
+      <c r="C23" s="90" t="n"/>
+      <c r="D23" s="90" t="n"/>
+      <c r="E23" s="91" t="n"/>
+      <c r="F23" s="92" t="n"/>
+      <c r="G23" s="92" t="n"/>
+      <c r="H23" s="92" t="n"/>
+      <c r="I23" s="92" t="n"/>
+      <c r="J23" s="89">
         <f>IF(OR(H23="",I23=""),"",VALUE(H23)*VALUE(I23))</f>
         <v/>
       </c>
-      <c r="K23" s="48">
+      <c r="K23" s="89">
         <f>IF(J23="","",IF(J23&gt;=15,"Alto",IF(J23&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L23" s="48">
+      <c r="L23" s="89">
         <f>IF(J23="","",IF(G23="Positivo","Positivo",IF(OR(K23="Alto",F23="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M23" s="46" t="n"/>
-      <c r="N23" s="46" t="n"/>
-      <c r="O23" s="83" t="n"/>
-      <c r="P23" s="22" t="n"/>
+      <c r="M23" s="90" t="n"/>
+      <c r="N23" s="90" t="n"/>
+      <c r="O23" s="84" t="n"/>
+      <c r="P23" s="86" t="n"/>
     </row>
     <row r="24" ht="36" customHeight="1" s="33">
-      <c r="A24" s="48" t="n">
+      <c r="A24" s="89" t="n">
         <v>9</v>
       </c>
-      <c r="B24" s="46" t="n"/>
-      <c r="C24" s="46" t="n"/>
-      <c r="D24" s="46" t="n"/>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="48" t="n"/>
-      <c r="G24" s="48" t="n"/>
-      <c r="H24" s="48" t="n"/>
-      <c r="I24" s="48" t="n"/>
-      <c r="J24" s="48">
+      <c r="B24" s="90" t="n"/>
+      <c r="C24" s="90" t="n"/>
+      <c r="D24" s="90" t="n"/>
+      <c r="E24" s="91" t="n"/>
+      <c r="F24" s="92" t="n"/>
+      <c r="G24" s="92" t="n"/>
+      <c r="H24" s="92" t="n"/>
+      <c r="I24" s="92" t="n"/>
+      <c r="J24" s="89">
         <f>IF(OR(H24="",I24=""),"",VALUE(H24)*VALUE(I24))</f>
         <v/>
       </c>
-      <c r="K24" s="48">
+      <c r="K24" s="89">
         <f>IF(J24="","",IF(J24&gt;=15,"Alto",IF(J24&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L24" s="48">
+      <c r="L24" s="89">
         <f>IF(J24="","",IF(G24="Positivo","Positivo",IF(OR(K24="Alto",F24="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M24" s="46" t="n"/>
-      <c r="N24" s="46" t="n"/>
-      <c r="O24" s="83" t="n"/>
-      <c r="P24" s="22" t="n"/>
+      <c r="M24" s="90" t="n"/>
+      <c r="N24" s="90" t="n"/>
+      <c r="O24" s="84" t="n"/>
+      <c r="P24" s="86" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="33">
-      <c r="A25" s="48" t="n">
+      <c r="A25" s="89" t="n">
         <v>10</v>
       </c>
-      <c r="B25" s="46" t="n"/>
-      <c r="C25" s="46" t="n"/>
-      <c r="D25" s="46" t="n"/>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="48" t="n"/>
-      <c r="G25" s="48" t="n"/>
-      <c r="H25" s="48" t="n"/>
-      <c r="I25" s="48" t="n"/>
-      <c r="J25" s="48">
+      <c r="B25" s="90" t="n"/>
+      <c r="C25" s="90" t="n"/>
+      <c r="D25" s="90" t="n"/>
+      <c r="E25" s="91" t="n"/>
+      <c r="F25" s="92" t="n"/>
+      <c r="G25" s="92" t="n"/>
+      <c r="H25" s="92" t="n"/>
+      <c r="I25" s="92" t="n"/>
+      <c r="J25" s="89">
         <f>IF(OR(H25="",I25=""),"",VALUE(H25)*VALUE(I25))</f>
         <v/>
       </c>
-      <c r="K25" s="48">
+      <c r="K25" s="89">
         <f>IF(J25="","",IF(J25&gt;=15,"Alto",IF(J25&gt;=8,"Medio","Bajo")))</f>
         <v/>
       </c>
-      <c r="L25" s="48">
+      <c r="L25" s="89">
         <f>IF(J25="","",IF(G25="Positivo","Positivo",IF(OR(K25="Alto",F25="Emergencia"),"Sí","No")))</f>
         <v/>
       </c>
-      <c r="M25" s="46" t="n"/>
-      <c r="N25" s="46" t="n"/>
-      <c r="O25" s="83" t="n"/>
-      <c r="P25" s="22" t="n"/>
+      <c r="M25" s="90" t="n"/>
+      <c r="N25" s="90" t="n"/>
+      <c r="O25" s="84" t="n"/>
+      <c r="P25" s="86" t="n"/>
     </row>
     <row r="26" ht="28.05" customHeight="1" s="33">
       <c r="A26" s="29" t="inlineStr">
@@ -3451,28 +3570,28 @@
         </is>
       </c>
       <c r="B30" s="20" t="n"/>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="20" t="n"/>
+      <c r="C30" s="90" t="n"/>
+      <c r="D30" s="95" t="n"/>
+      <c r="E30" s="96" t="n"/>
       <c r="F30" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="G30" s="20" t="n"/>
-      <c r="H30" s="23" t="n"/>
-      <c r="I30" s="24" t="n"/>
-      <c r="J30" s="24" t="n"/>
-      <c r="K30" s="20" t="n"/>
+      <c r="H30" s="90" t="n"/>
+      <c r="I30" s="95" t="n"/>
+      <c r="J30" s="95" t="n"/>
+      <c r="K30" s="96" t="n"/>
       <c r="L30" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="M30" s="20" t="n"/>
-      <c r="N30" s="23" t="n"/>
-      <c r="O30" s="24" t="n"/>
-      <c r="P30" s="20" t="n"/>
+      <c r="N30" s="90" t="n"/>
+      <c r="O30" s="95" t="n"/>
+      <c r="P30" s="96" t="n"/>
     </row>
     <row r="31" ht="21" customHeight="1" s="33">
       <c r="A31" s="19" t="inlineStr">
@@ -3481,28 +3600,28 @@
         </is>
       </c>
       <c r="B31" s="20" t="n"/>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="24" t="n"/>
-      <c r="E31" s="20" t="n"/>
+      <c r="C31" s="90" t="n"/>
+      <c r="D31" s="95" t="n"/>
+      <c r="E31" s="96" t="n"/>
       <c r="F31" s="19" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="G31" s="20" t="n"/>
-      <c r="H31" s="23" t="n"/>
-      <c r="I31" s="24" t="n"/>
-      <c r="J31" s="24" t="n"/>
-      <c r="K31" s="20" t="n"/>
+      <c r="H31" s="90" t="n"/>
+      <c r="I31" s="95" t="n"/>
+      <c r="J31" s="95" t="n"/>
+      <c r="K31" s="96" t="n"/>
       <c r="L31" s="19" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="M31" s="20" t="n"/>
-      <c r="N31" s="23" t="n"/>
-      <c r="O31" s="24" t="n"/>
-      <c r="P31" s="20" t="n"/>
+      <c r="N31" s="90" t="n"/>
+      <c r="O31" s="95" t="n"/>
+      <c r="P31" s="96" t="n"/>
     </row>
     <row r="32" ht="21" customHeight="1" s="33">
       <c r="A32" s="19" t="inlineStr">
@@ -3511,28 +3630,28 @@
         </is>
       </c>
       <c r="B32" s="20" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="20" t="n"/>
+      <c r="C32" s="90" t="n"/>
+      <c r="D32" s="95" t="n"/>
+      <c r="E32" s="96" t="n"/>
       <c r="F32" s="19" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="G32" s="20" t="n"/>
-      <c r="H32" s="23" t="n"/>
-      <c r="I32" s="24" t="n"/>
-      <c r="J32" s="24" t="n"/>
-      <c r="K32" s="20" t="n"/>
+      <c r="H32" s="90" t="n"/>
+      <c r="I32" s="95" t="n"/>
+      <c r="J32" s="95" t="n"/>
+      <c r="K32" s="96" t="n"/>
       <c r="L32" s="19" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="M32" s="20" t="n"/>
-      <c r="N32" s="23" t="n"/>
-      <c r="O32" s="24" t="n"/>
-      <c r="P32" s="20" t="n"/>
+      <c r="N32" s="90" t="n"/>
+      <c r="O32" s="95" t="n"/>
+      <c r="P32" s="96" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -3546,6 +3665,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="61">
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A30:B30"/>
